--- a/baseline/T2vsAI_baseline_metrics_summary.xlsx
+++ b/baseline/T2vsAI_baseline_metrics_summary.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H31"/>
+  <dimension ref="A1:H37"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -483,20 +483,20 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>AI</t>
+          <t>T2</t>
         </is>
       </c>
       <c r="D2" t="n">
         <v>52</v>
       </c>
       <c r="E2" t="n">
-        <v>0.2055847834884663</v>
+        <v>0.1446164672765659</v>
       </c>
       <c r="F2" t="n">
-        <v>1.442307692307692</v>
+        <v>1.557692307692308</v>
       </c>
       <c r="G2" t="n">
-        <v>0.5384615384615384</v>
+        <v>0.4807692307692308</v>
       </c>
       <c r="H2" t="inlineStr"/>
     </row>
@@ -513,20 +513,20 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>T2</t>
+          <t>AI</t>
         </is>
       </c>
       <c r="D3" t="n">
         <v>52</v>
       </c>
       <c r="E3" t="n">
-        <v>0.1446164672765659</v>
+        <v>0.2055847834884663</v>
       </c>
       <c r="F3" t="n">
-        <v>1.557692307692308</v>
+        <v>1.442307692307692</v>
       </c>
       <c r="G3" t="n">
-        <v>0.4807692307692308</v>
+        <v>0.5384615384615384</v>
       </c>
       <c r="H3" t="inlineStr"/>
     </row>
@@ -538,27 +538,23 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>baseline_jaccard</t>
+          <t>baseline_concept</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>AI</t>
+          <t>T2+AI+baseline (Krippendorff alpha)</t>
         </is>
       </c>
       <c r="D4" t="n">
-        <v>52</v>
-      </c>
-      <c r="E4" t="n">
-        <v>0.02075919335705823</v>
-      </c>
-      <c r="F4" t="n">
-        <v>2.076923076923077</v>
-      </c>
-      <c r="G4" t="n">
-        <v>0.2115384615384615</v>
-      </c>
-      <c r="H4" t="inlineStr"/>
+        <v>55</v>
+      </c>
+      <c r="E4" t="inlineStr"/>
+      <c r="F4" t="inlineStr"/>
+      <c r="G4" t="inlineStr"/>
+      <c r="H4" t="n">
+        <v>0.2028405989049858</v>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -598,53 +594,53 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>baseline_concept</t>
+          <t>baseline_jaccard</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>AI+T2+baseline (Krippendorff alpha)</t>
+          <t>AI</t>
         </is>
       </c>
       <c r="D6" t="n">
-        <v>55</v>
-      </c>
-      <c r="E6" t="inlineStr"/>
-      <c r="F6" t="inlineStr"/>
-      <c r="G6" t="inlineStr"/>
-      <c r="H6" t="n">
-        <v>0.2028405989049858</v>
-      </c>
+        <v>52</v>
+      </c>
+      <c r="E6" t="n">
+        <v>0.02075919335705823</v>
+      </c>
+      <c r="F6" t="n">
+        <v>2.076923076923077</v>
+      </c>
+      <c r="G6" t="n">
+        <v>0.2115384615384615</v>
+      </c>
+      <c r="H6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Student 2</t>
+          <t>Student 1</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>baseline_concept</t>
+          <t>baseline_jaccard</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>AI</t>
+          <t>T2+AI+baseline (Krippendorff alpha)</t>
         </is>
       </c>
       <c r="D7" t="n">
-        <v>52</v>
-      </c>
-      <c r="E7" t="n">
-        <v>0.1757772810404389</v>
-      </c>
-      <c r="F7" t="n">
-        <v>1.346153846153846</v>
-      </c>
-      <c r="G7" t="n">
-        <v>0.6346153846153846</v>
-      </c>
-      <c r="H7" t="inlineStr"/>
+        <v>55</v>
+      </c>
+      <c r="E7" t="inlineStr"/>
+      <c r="F7" t="inlineStr"/>
+      <c r="G7" t="inlineStr"/>
+      <c r="H7" t="n">
+        <v>-0.07387093689432356</v>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -684,7 +680,7 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>baseline_jaccard</t>
+          <t>baseline_concept</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
@@ -696,13 +692,13 @@
         <v>52</v>
       </c>
       <c r="E9" t="n">
-        <v>0.04635036496350353</v>
+        <v>0.1757772810404389</v>
       </c>
       <c r="F9" t="n">
-        <v>1.673076923076923</v>
+        <v>1.346153846153846</v>
       </c>
       <c r="G9" t="n">
-        <v>0.5192307692307693</v>
+        <v>0.6346153846153846</v>
       </c>
       <c r="H9" t="inlineStr"/>
     </row>
@@ -714,27 +710,23 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>baseline_jaccard</t>
+          <t>baseline_concept</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>T2</t>
+          <t>T2+AI+baseline (Krippendorff alpha)</t>
         </is>
       </c>
       <c r="D10" t="n">
-        <v>52</v>
-      </c>
-      <c r="E10" t="n">
-        <v>0.08429561200923785</v>
-      </c>
-      <c r="F10" t="n">
-        <v>1.596153846153846</v>
-      </c>
-      <c r="G10" t="n">
-        <v>0.5384615384615384</v>
-      </c>
-      <c r="H10" t="inlineStr"/>
+        <v>55</v>
+      </c>
+      <c r="E10" t="inlineStr"/>
+      <c r="F10" t="inlineStr"/>
+      <c r="G10" t="inlineStr"/>
+      <c r="H10" t="n">
+        <v>0.2462117330005289</v>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -744,33 +736,37 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>baseline_concept</t>
+          <t>baseline_jaccard</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>AI+T2+baseline (Krippendorff alpha)</t>
+          <t>T2</t>
         </is>
       </c>
       <c r="D11" t="n">
-        <v>55</v>
-      </c>
-      <c r="E11" t="inlineStr"/>
-      <c r="F11" t="inlineStr"/>
-      <c r="G11" t="inlineStr"/>
-      <c r="H11" t="n">
-        <v>0.2462117330005289</v>
-      </c>
+        <v>52</v>
+      </c>
+      <c r="E11" t="n">
+        <v>0.08429561200923785</v>
+      </c>
+      <c r="F11" t="n">
+        <v>1.596153846153846</v>
+      </c>
+      <c r="G11" t="n">
+        <v>0.5384615384615384</v>
+      </c>
+      <c r="H11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Student 3</t>
+          <t>Student 2</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>baseline_concept</t>
+          <t>baseline_jaccard</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
@@ -782,45 +778,41 @@
         <v>52</v>
       </c>
       <c r="E12" t="n">
-        <v>0.1205269716930746</v>
+        <v>0.04635036496350353</v>
       </c>
       <c r="F12" t="n">
-        <v>1.576923076923077</v>
+        <v>1.673076923076923</v>
       </c>
       <c r="G12" t="n">
-        <v>0.5</v>
+        <v>0.5192307692307693</v>
       </c>
       <c r="H12" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Student 3</t>
+          <t>Student 2</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>baseline_concept</t>
+          <t>baseline_jaccard</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>T2</t>
+          <t>T2+AI+baseline (Krippendorff alpha)</t>
         </is>
       </c>
       <c r="D13" t="n">
-        <v>52</v>
-      </c>
-      <c r="E13" t="n">
-        <v>0.1359359359359358</v>
-      </c>
-      <c r="F13" t="n">
-        <v>1.423076923076923</v>
-      </c>
-      <c r="G13" t="n">
-        <v>0.5384615384615384</v>
-      </c>
-      <c r="H13" t="inlineStr"/>
+        <v>55</v>
+      </c>
+      <c r="E13" t="inlineStr"/>
+      <c r="F13" t="inlineStr"/>
+      <c r="G13" t="inlineStr"/>
+      <c r="H13" t="n">
+        <v>0.08517415188785538</v>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
@@ -830,25 +822,25 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>baseline_jaccard</t>
+          <t>baseline_concept</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>AI</t>
+          <t>T2</t>
         </is>
       </c>
       <c r="D14" t="n">
         <v>52</v>
       </c>
       <c r="E14" t="n">
-        <v>0.0523917995444193</v>
+        <v>0.1359359359359358</v>
       </c>
       <c r="F14" t="n">
-        <v>2.076923076923077</v>
+        <v>1.423076923076923</v>
       </c>
       <c r="G14" t="n">
-        <v>0.1923076923076923</v>
+        <v>0.5384615384615384</v>
       </c>
       <c r="H14" t="inlineStr"/>
     </row>
@@ -860,25 +852,25 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>baseline_jaccard</t>
+          <t>baseline_concept</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>T2</t>
+          <t>AI</t>
         </is>
       </c>
       <c r="D15" t="n">
         <v>52</v>
       </c>
       <c r="E15" t="n">
-        <v>0.06870464721321601</v>
+        <v>0.1205269716930746</v>
       </c>
       <c r="F15" t="n">
-        <v>1.846153846153846</v>
+        <v>1.576923076923077</v>
       </c>
       <c r="G15" t="n">
-        <v>0.3076923076923077</v>
+        <v>0.5</v>
       </c>
       <c r="H15" t="inlineStr"/>
     </row>
@@ -895,7 +887,7 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>AI+T2+baseline (Krippendorff alpha)</t>
+          <t>T2+AI+baseline (Krippendorff alpha)</t>
         </is>
       </c>
       <c r="D16" t="n">
@@ -911,67 +903,67 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Student 4</t>
+          <t>Student 3</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>baseline_concept</t>
+          <t>baseline_jaccard</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>AI</t>
+          <t>T2</t>
         </is>
       </c>
       <c r="D17" t="n">
         <v>52</v>
       </c>
       <c r="E17" t="n">
-        <v>0.3907396950875212</v>
+        <v>0.06870464721321601</v>
       </c>
       <c r="F17" t="n">
-        <v>0.8653846153846154</v>
+        <v>1.846153846153846</v>
       </c>
       <c r="G17" t="n">
-        <v>0.75</v>
+        <v>0.3076923076923077</v>
       </c>
       <c r="H17" t="inlineStr"/>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>Student 4</t>
+          <t>Student 3</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>baseline_concept</t>
+          <t>baseline_jaccard</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>T2</t>
+          <t>AI</t>
         </is>
       </c>
       <c r="D18" t="n">
         <v>52</v>
       </c>
       <c r="E18" t="n">
-        <v>0.4234507897934386</v>
+        <v>0.0523917995444193</v>
       </c>
       <c r="F18" t="n">
-        <v>0.75</v>
+        <v>2.076923076923077</v>
       </c>
       <c r="G18" t="n">
-        <v>0.7884615384615384</v>
+        <v>0.1923076923076923</v>
       </c>
       <c r="H18" t="inlineStr"/>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>Student 4</t>
+          <t>Student 3</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -981,22 +973,18 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>AI</t>
+          <t>T2+AI+baseline (Krippendorff alpha)</t>
         </is>
       </c>
       <c r="D19" t="n">
-        <v>52</v>
-      </c>
-      <c r="E19" t="n">
-        <v>0.2425847457627117</v>
-      </c>
-      <c r="F19" t="n">
-        <v>1.115384615384615</v>
-      </c>
-      <c r="G19" t="n">
-        <v>0.6923076923076923</v>
-      </c>
-      <c r="H19" t="inlineStr"/>
+        <v>55</v>
+      </c>
+      <c r="E19" t="inlineStr"/>
+      <c r="F19" t="inlineStr"/>
+      <c r="G19" t="inlineStr"/>
+      <c r="H19" t="n">
+        <v>0.03907309773309098</v>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
@@ -1006,7 +994,7 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>baseline_jaccard</t>
+          <t>baseline_concept</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
@@ -1018,13 +1006,13 @@
         <v>52</v>
       </c>
       <c r="E20" t="n">
-        <v>0.2803297997644287</v>
+        <v>0.4234507897934386</v>
       </c>
       <c r="F20" t="n">
-        <v>0.9615384615384616</v>
+        <v>0.75</v>
       </c>
       <c r="G20" t="n">
-        <v>0.7307692307692307</v>
+        <v>0.7884615384615384</v>
       </c>
       <c r="H20" t="inlineStr"/>
     </row>
@@ -1041,23 +1029,27 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>AI+T2+baseline (Krippendorff alpha)</t>
+          <t>AI</t>
         </is>
       </c>
       <c r="D21" t="n">
-        <v>55</v>
-      </c>
-      <c r="E21" t="inlineStr"/>
-      <c r="F21" t="inlineStr"/>
-      <c r="G21" t="inlineStr"/>
-      <c r="H21" t="n">
-        <v>0.4838962966498886</v>
-      </c>
+        <v>52</v>
+      </c>
+      <c r="E21" t="n">
+        <v>0.3907396950875212</v>
+      </c>
+      <c r="F21" t="n">
+        <v>0.8653846153846154</v>
+      </c>
+      <c r="G21" t="n">
+        <v>0.75</v>
+      </c>
+      <c r="H21" t="inlineStr"/>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>Student 5</t>
+          <t>Student 4</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -1067,32 +1059,28 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>AI</t>
+          <t>T2+AI+baseline (Krippendorff alpha)</t>
         </is>
       </c>
       <c r="D22" t="n">
-        <v>52</v>
-      </c>
-      <c r="E22" t="n">
-        <v>0.02748091603053437</v>
-      </c>
-      <c r="F22" t="n">
-        <v>2.192307692307693</v>
-      </c>
-      <c r="G22" t="n">
-        <v>0.1923076923076923</v>
-      </c>
-      <c r="H22" t="inlineStr"/>
+        <v>55</v>
+      </c>
+      <c r="E22" t="inlineStr"/>
+      <c r="F22" t="inlineStr"/>
+      <c r="G22" t="inlineStr"/>
+      <c r="H22" t="n">
+        <v>0.4838962966498886</v>
+      </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>Student 5</t>
+          <t>Student 4</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>baseline_concept</t>
+          <t>baseline_jaccard</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
@@ -1104,20 +1092,20 @@
         <v>52</v>
       </c>
       <c r="E23" t="n">
-        <v>0.0239324260910373</v>
+        <v>0.2803297997644287</v>
       </c>
       <c r="F23" t="n">
-        <v>2.230769230769231</v>
+        <v>0.9615384615384616</v>
       </c>
       <c r="G23" t="n">
-        <v>0.2307692307692308</v>
+        <v>0.7307692307692307</v>
       </c>
       <c r="H23" t="inlineStr"/>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>Student 5</t>
+          <t>Student 4</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -1134,20 +1122,20 @@
         <v>52</v>
       </c>
       <c r="E24" t="n">
-        <v>0.007788161993769527</v>
+        <v>0.2425847457627117</v>
       </c>
       <c r="F24" t="n">
-        <v>2.230769230769231</v>
+        <v>1.115384615384615</v>
       </c>
       <c r="G24" t="n">
-        <v>0.1730769230769231</v>
+        <v>0.6923076923076923</v>
       </c>
       <c r="H24" t="inlineStr"/>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>Student 5</t>
+          <t>Student 4</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -1157,22 +1145,18 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>T2</t>
+          <t>T2+AI+baseline (Krippendorff alpha)</t>
         </is>
       </c>
       <c r="D25" t="n">
-        <v>52</v>
-      </c>
-      <c r="E25" t="n">
-        <v>0.02437858508604218</v>
-      </c>
-      <c r="F25" t="n">
-        <v>2.230769230769231</v>
-      </c>
-      <c r="G25" t="n">
-        <v>0.2115384615384615</v>
-      </c>
-      <c r="H25" t="inlineStr"/>
+        <v>55</v>
+      </c>
+      <c r="E25" t="inlineStr"/>
+      <c r="F25" t="inlineStr"/>
+      <c r="G25" t="inlineStr"/>
+      <c r="H25" t="n">
+        <v>0.3422132648813736</v>
+      </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
@@ -1187,23 +1171,27 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>AI+T2+baseline (Krippendorff alpha)</t>
+          <t>T2</t>
         </is>
       </c>
       <c r="D26" t="n">
-        <v>55</v>
-      </c>
-      <c r="E26" t="inlineStr"/>
-      <c r="F26" t="inlineStr"/>
-      <c r="G26" t="inlineStr"/>
-      <c r="H26" t="n">
-        <v>-0.1686613902964824</v>
-      </c>
+        <v>52</v>
+      </c>
+      <c r="E26" t="n">
+        <v>0.0239324260910373</v>
+      </c>
+      <c r="F26" t="n">
+        <v>2.230769230769231</v>
+      </c>
+      <c r="G26" t="n">
+        <v>0.2307692307692308</v>
+      </c>
+      <c r="H26" t="inlineStr"/>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>Student 6</t>
+          <t>Student 5</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
@@ -1220,20 +1208,20 @@
         <v>52</v>
       </c>
       <c r="E27" t="n">
-        <v>0.128644424406372</v>
+        <v>0.02748091603053437</v>
       </c>
       <c r="F27" t="n">
-        <v>1.596153846153846</v>
+        <v>2.192307692307693</v>
       </c>
       <c r="G27" t="n">
-        <v>0.4615384615384616</v>
+        <v>0.1923076923076923</v>
       </c>
       <c r="H27" t="inlineStr"/>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>Student 6</t>
+          <t>Student 5</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
@@ -1243,27 +1231,23 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>T2</t>
+          <t>T2+AI+baseline (Krippendorff alpha)</t>
         </is>
       </c>
       <c r="D28" t="n">
-        <v>52</v>
-      </c>
-      <c r="E28" t="n">
-        <v>0.107768691588785</v>
-      </c>
-      <c r="F28" t="n">
-        <v>1.75</v>
-      </c>
-      <c r="G28" t="n">
-        <v>0.3846153846153846</v>
-      </c>
-      <c r="H28" t="inlineStr"/>
+        <v>55</v>
+      </c>
+      <c r="E28" t="inlineStr"/>
+      <c r="F28" t="inlineStr"/>
+      <c r="G28" t="inlineStr"/>
+      <c r="H28" t="n">
+        <v>-0.1686613902964824</v>
+      </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>Student 6</t>
+          <t>Student 5</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
@@ -1273,27 +1257,27 @@
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>AI</t>
+          <t>T2</t>
         </is>
       </c>
       <c r="D29" t="n">
         <v>52</v>
       </c>
       <c r="E29" t="n">
-        <v>0.1518987341772152</v>
+        <v>0.02437858508604218</v>
       </c>
       <c r="F29" t="n">
-        <v>0.8653846153846154</v>
+        <v>2.230769230769231</v>
       </c>
       <c r="G29" t="n">
-        <v>0.7884615384615384</v>
+        <v>0.2115384615384615</v>
       </c>
       <c r="H29" t="inlineStr"/>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>Student 6</t>
+          <t>Student 5</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
@@ -1303,37 +1287,37 @@
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>T2</t>
+          <t>AI</t>
         </is>
       </c>
       <c r="D30" t="n">
         <v>52</v>
       </c>
       <c r="E30" t="n">
-        <v>0.07352941176470584</v>
+        <v>0.007788161993769527</v>
       </c>
       <c r="F30" t="n">
-        <v>0.7884615384615384</v>
+        <v>2.230769230769231</v>
       </c>
       <c r="G30" t="n">
-        <v>0.8269230769230769</v>
+        <v>0.1730769230769231</v>
       </c>
       <c r="H30" t="inlineStr"/>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>Student 6</t>
+          <t>Student 5</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>baseline_concept</t>
+          <t>baseline_jaccard</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>AI+T2+baseline (Krippendorff alpha)</t>
+          <t>T2+AI+baseline (Krippendorff alpha)</t>
         </is>
       </c>
       <c r="D31" t="n">
@@ -1343,7 +1327,179 @@
       <c r="F31" t="inlineStr"/>
       <c r="G31" t="inlineStr"/>
       <c r="H31" t="n">
+        <v>-0.1862475672454564</v>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="inlineStr">
+        <is>
+          <t>Student 6</t>
+        </is>
+      </c>
+      <c r="B32" t="inlineStr">
+        <is>
+          <t>baseline_concept</t>
+        </is>
+      </c>
+      <c r="C32" t="inlineStr">
+        <is>
+          <t>T2</t>
+        </is>
+      </c>
+      <c r="D32" t="n">
+        <v>52</v>
+      </c>
+      <c r="E32" t="n">
+        <v>0.107768691588785</v>
+      </c>
+      <c r="F32" t="n">
+        <v>1.75</v>
+      </c>
+      <c r="G32" t="n">
+        <v>0.3846153846153846</v>
+      </c>
+      <c r="H32" t="inlineStr"/>
+    </row>
+    <row r="33">
+      <c r="A33" t="inlineStr">
+        <is>
+          <t>Student 6</t>
+        </is>
+      </c>
+      <c r="B33" t="inlineStr">
+        <is>
+          <t>baseline_concept</t>
+        </is>
+      </c>
+      <c r="C33" t="inlineStr">
+        <is>
+          <t>AI</t>
+        </is>
+      </c>
+      <c r="D33" t="n">
+        <v>52</v>
+      </c>
+      <c r="E33" t="n">
+        <v>0.128644424406372</v>
+      </c>
+      <c r="F33" t="n">
+        <v>1.596153846153846</v>
+      </c>
+      <c r="G33" t="n">
+        <v>0.4615384615384616</v>
+      </c>
+      <c r="H33" t="inlineStr"/>
+    </row>
+    <row r="34">
+      <c r="A34" t="inlineStr">
+        <is>
+          <t>Student 6</t>
+        </is>
+      </c>
+      <c r="B34" t="inlineStr">
+        <is>
+          <t>baseline_concept</t>
+        </is>
+      </c>
+      <c r="C34" t="inlineStr">
+        <is>
+          <t>T2+AI+baseline (Krippendorff alpha)</t>
+        </is>
+      </c>
+      <c r="D34" t="n">
+        <v>55</v>
+      </c>
+      <c r="E34" t="inlineStr"/>
+      <c r="F34" t="inlineStr"/>
+      <c r="G34" t="inlineStr"/>
+      <c r="H34" t="n">
         <v>0.1029709523760195</v>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="inlineStr">
+        <is>
+          <t>Student 6</t>
+        </is>
+      </c>
+      <c r="B35" t="inlineStr">
+        <is>
+          <t>baseline_jaccard</t>
+        </is>
+      </c>
+      <c r="C35" t="inlineStr">
+        <is>
+          <t>T2</t>
+        </is>
+      </c>
+      <c r="D35" t="n">
+        <v>52</v>
+      </c>
+      <c r="E35" t="n">
+        <v>0.07352941176470584</v>
+      </c>
+      <c r="F35" t="n">
+        <v>0.7884615384615384</v>
+      </c>
+      <c r="G35" t="n">
+        <v>0.8269230769230769</v>
+      </c>
+      <c r="H35" t="inlineStr"/>
+    </row>
+    <row r="36">
+      <c r="A36" t="inlineStr">
+        <is>
+          <t>Student 6</t>
+        </is>
+      </c>
+      <c r="B36" t="inlineStr">
+        <is>
+          <t>baseline_jaccard</t>
+        </is>
+      </c>
+      <c r="C36" t="inlineStr">
+        <is>
+          <t>AI</t>
+        </is>
+      </c>
+      <c r="D36" t="n">
+        <v>52</v>
+      </c>
+      <c r="E36" t="n">
+        <v>0.1518987341772152</v>
+      </c>
+      <c r="F36" t="n">
+        <v>0.8653846153846154</v>
+      </c>
+      <c r="G36" t="n">
+        <v>0.7884615384615384</v>
+      </c>
+      <c r="H36" t="inlineStr"/>
+    </row>
+    <row r="37">
+      <c r="A37" t="inlineStr">
+        <is>
+          <t>Student 6</t>
+        </is>
+      </c>
+      <c r="B37" t="inlineStr">
+        <is>
+          <t>baseline_jaccard</t>
+        </is>
+      </c>
+      <c r="C37" t="inlineStr">
+        <is>
+          <t>T2+AI+baseline (Krippendorff alpha)</t>
+        </is>
+      </c>
+      <c r="D37" t="n">
+        <v>55</v>
+      </c>
+      <c r="E37" t="inlineStr"/>
+      <c r="F37" t="inlineStr"/>
+      <c r="G37" t="inlineStr"/>
+      <c r="H37" t="n">
+        <v>0.2837748873864552</v>
       </c>
     </row>
   </sheetData>
